--- a/outputs/2026-10-04_sttv_linea-base-sast.xlsx
+++ b/outputs/2026-10-04_sttv_linea-base-sast.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -514,75 +514,82 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Periodo de línea base (formato ANSV): sep 2023 a ago 2026, 36 meses (Año 1, 2 y 3) previos al inicio de operación.</t>
+          <t>Periodo de línea base (formato ANSV): los 36 meses (Año 1, 2 y 3) previos al mes de inicio de operación de cada equipo (plataforma ANSV): EQUIPO021 inicio 02/09/2026 → sep 2023 a ago 2026; EQUIPO022 inicio 02/09/2026 → sep 2023 a ago 2026; EQUIPO031 inicio 27/08/2026 → ago 2023 a jul 2026; EQUIPO032 inicio 27/08/2026 → ago 2023 a jul 2026; EQUIPO041 inicio 18/08/2026 → ago 2023 a jul 2026; EQUIPO042 inicio 17/06/2026 → jun 2023 a may 2026; EQUIPO051 inicio 27/08/2026 → ago 2023 a jul 2026; EQUIPO052 inicio 27/08/2026 → ago 2023 a jul 2026; EQUIPO071 inicio 02/10/2026 → oct 2023 a sep 2026. Los totales por punto usan la ventana del equipo del punto que inició primero.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Zona: polígono de la capa «Zona de influencia» del SIG de equipos SAST. Criterio oficial mixto: los comparendos ubicados por dirección (punto sobre el eje de la vía) cuentan si caen dentro del polígono; los siniestros y los comparendos ubicados por GPS (pueden caer fuera de la calzada), si caen a ≤ 15 m del polígono. Distancias en EPSG:9377 (CTM12). Las cifras con todo estricto y todo +15 m están en Observaciones y en «Resumen».</t>
+          <t>Equipos: coordenadas, códigos aprobados y nombres del Excel «Equipos SAST»; fecha de inicio, código único, solicitud y dirección de la plataforma ANSV (config/equipos.yaml). Los comparendos de las cámaras SAST se asignan a su equipo por la dirección de la plataforma y se ubican en la coordenada del equipo.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Fallecidos y lesionados: personas (cantidad_muertos, cantidad_heridos) de los siniestros georreferenciados del portal ANSV «Siniestralidad Valledupar», corte 2026-10-06.</t>
+          <t>Zona: polígono de la capa «Zona de influencia» del SIG de equipos SAST. Criterio oficial mixto: los comparendos ubicados por dirección (punto sobre el eje de la vía) cuentan si caen dentro del polígono; los siniestros y los comparendos ubicados por GPS (pueden caer fuera de la calzada), si caen a ≤ 15 m del polígono. Distancias en EPSG:9377 (CTM12). Las cifras con todo estricto y todo +15 m están en Observaciones y en «Resumen».</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Comparendos: export del sistema de comparendos 01/01/2023–04/10/2026. Se cuentan los impuestos por agentes y por la fotodetección previa (no SAST), por código; los generados por las cámaras SAST se excluyen de la línea base (hoja «SAST inicio»).</t>
+          <t>Fallecidos y lesionados: personas (cantidad_muertos, cantidad_heridos) de los siniestros georreferenciados del portal ANSV «Siniestralidad Valledupar», corte 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Ubicación de comparendos: manda la dirección del comparendo, geocodificada sobre los ejes viales IGAC 2021 + OSM (cruce o placa domiciliaria). La coordenada GPS de la comparendera solo se usa si la dirección no da un punto y la coordenada cae en la cabecera; discrepancias GPS–dirección &gt; 100 m quedan marcadas.</t>
+          <t>Comparendos: export del sistema de comparendos 01/01/2023–04/10/2026. Se cuentan los impuestos por agentes y por la fotodetección previa (no SAST), por código; los generados por las cámaras SAST se excluyen de la línea base (hoja «SAST inicio»).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Un evento en zonas de dos equipos cuenta para cada equipo; la hoja «Por punto» cuenta sin doble conteo.</t>
+          <t>Ubicación de comparendos: manda la dirección del comparendo, geocodificada sobre los ejes viales IGAC 2021 + OSM (cruce o placa domiciliaria). La coordenada GPS de la comparendera solo se usa si la dirección no da un punto y la coordenada cae en la cabecera; discrepancias GPS–dirección &gt; 100 m quedan marcadas.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cada hoja de equipo lista solo los códigos de infracción aprobados para ese equipo (Excel «Equipos SAST»).</t>
+          <t>Un evento en zonas de dos equipos cuenta para cada equipo; la hoja «Por punto» cuenta sin doble conteo.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ADVERTENCIA: el portal registra en 2026 muchos más lesionados por mes que en 2023–2025 (7.0 a 29.0 por mes en todo el municipio). La diferencia corresponde a un cambio en la captura, no necesariamente en la siniestralidad: la línea base de lesionados no es homogénea: los Años 1 y 2 y la primera parte del Año 3 (sep-2025 a ene-2026) pueden estar subestimados.</t>
+          <t>Cada hoja de equipo lista solo los códigos de infracción aprobados para ese equipo (Excel «Equipos SAST»).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ADVERTENCIA — fallecidos: la mezcla de fuentes del portal cambia entre años (Deceso clínico desde 2024, Geoportal y Policía hasta 2024, Mesa calidad solo 2025); puede haber subregistro o doble conteo.</t>
+          <t>ADVERTENCIA: el portal registra en 2026 muchos más lesionados por mes que en 2023–2025 (7.0 a 29.0 por mes en todo el municipio). La diferencia corresponde a un cambio en la captura, no necesariamente en la siniestralidad: la línea base de lesionados no es homogénea: los Años 1 y 2 y la primera parte del Año 3 (sep-2025 a ene-2026) pueden estar subestimados.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ADVERTENCIA — siniestros en zona: se ubican solo por la coordenada del portal y requieren revisión manual (hoja «Siniestros en zona», con posibles gemelos «Deceso clínico») antes de reportarse.</t>
+          <t>ADVERTENCIA — fallecidos: la mezcla de fuentes del portal cambia entre años (Deceso clínico desde 2024, Geoportal y Policía hasta 2024, Mesa calidad solo 2025); puede haber subregistro o doble conteo.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ADVERTENCIA — siniestros en zona: se ubican solo por la coordenada del portal y requieren revisión manual (hoja «Siniestros en zona», con posibles gemelos «Deceso clínico») antes de reportarse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>LIMITACIÓN — placas sin «#» («CARRERA 16 20-27»): se interpretan como domiciliarias; la regla solo pudo contrastarse con GPS en una minoría de registros (la fotodetección previa no trae coordenada).</t>
         </is>
@@ -659,7 +666,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 02/10/2026    Código único: CU000000000894    Solicitud: SOL0000010785    Dirección ANSV: CALLE 6 - CARRERA 23 (SENTIDO OESTE - ESTE)</t>
         </is>
       </c>
     </row>
@@ -700,182 +707,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Septiembre 2023</t>
+          <t>Octubre 2023</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Octubre 2023</t>
+          <t>Noviembre 2023</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Noviembre 2023</t>
+          <t>Diciembre 2023</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Diciembre 2023</t>
+          <t>Enero 2024</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Enero 2024</t>
+          <t>Febrero 2024</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Febrero 2024</t>
+          <t>Marzo 2024</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>Marzo 2024</t>
+          <t>Abril 2024</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Abril 2024</t>
+          <t>Mayo 2024</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Mayo 2024</t>
+          <t>Junio 2024</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Junio 2024</t>
+          <t>Julio 2024</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>Julio 2024</t>
+          <t>Agosto 2024</t>
         </is>
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Agosto 2024</t>
+          <t>Septiembre 2024</t>
         </is>
       </c>
       <c r="N7" s="5" t="inlineStr">
         <is>
-          <t>Septiembre 2024</t>
+          <t>Octubre 2024</t>
         </is>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>Octubre 2024</t>
+          <t>Noviembre 2024</t>
         </is>
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>Noviembre 2024</t>
+          <t>Diciembre 2024</t>
         </is>
       </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
-          <t>Diciembre 2024</t>
+          <t>Enero 2025</t>
         </is>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
-          <t>Enero 2025</t>
+          <t>Febrero 2025</t>
         </is>
       </c>
       <c r="S7" s="5" t="inlineStr">
         <is>
-          <t>Febrero 2025</t>
+          <t>Marzo 2025</t>
         </is>
       </c>
       <c r="T7" s="5" t="inlineStr">
         <is>
-          <t>Marzo 2025</t>
+          <t>Abril 2025</t>
         </is>
       </c>
       <c r="U7" s="5" t="inlineStr">
         <is>
-          <t>Abril 2025</t>
+          <t>Mayo 2025</t>
         </is>
       </c>
       <c r="V7" s="5" t="inlineStr">
         <is>
-          <t>Mayo 2025</t>
+          <t>Junio 2025</t>
         </is>
       </c>
       <c r="W7" s="5" t="inlineStr">
         <is>
-          <t>Junio 2025</t>
+          <t>Julio 2025</t>
         </is>
       </c>
       <c r="X7" s="5" t="inlineStr">
         <is>
-          <t>Julio 2025</t>
+          <t>Agosto 2025</t>
         </is>
       </c>
       <c r="Y7" s="5" t="inlineStr">
         <is>
-          <t>Agosto 2025</t>
+          <t>Septiembre 2025</t>
         </is>
       </c>
       <c r="Z7" s="5" t="inlineStr">
         <is>
-          <t>Septiembre 2025</t>
+          <t>Octubre 2025</t>
         </is>
       </c>
       <c r="AA7" s="5" t="inlineStr">
         <is>
-          <t>Octubre 2025</t>
+          <t>Noviembre 2025</t>
         </is>
       </c>
       <c r="AB7" s="5" t="inlineStr">
         <is>
-          <t>Noviembre 2025</t>
+          <t>Diciembre 2025</t>
         </is>
       </c>
       <c r="AC7" s="5" t="inlineStr">
         <is>
-          <t>Diciembre 2025</t>
+          <t>Enero 2026</t>
         </is>
       </c>
       <c r="AD7" s="5" t="inlineStr">
         <is>
-          <t>Enero 2026</t>
+          <t>Febrero 2026</t>
         </is>
       </c>
       <c r="AE7" s="5" t="inlineStr">
         <is>
-          <t>Febrero 2026</t>
+          <t>Marzo 2026</t>
         </is>
       </c>
       <c r="AF7" s="5" t="inlineStr">
         <is>
-          <t>Marzo 2026</t>
+          <t>Abril 2026</t>
         </is>
       </c>
       <c r="AG7" s="5" t="inlineStr">
         <is>
-          <t>Abril 2026</t>
+          <t>Mayo 2026</t>
         </is>
       </c>
       <c r="AH7" s="5" t="inlineStr">
         <is>
-          <t>Mayo 2026</t>
+          <t>Junio 2026</t>
         </is>
       </c>
       <c r="AI7" s="5" t="inlineStr">
         <is>
-          <t>Junio 2026</t>
+          <t>Julio 2026</t>
         </is>
       </c>
       <c r="AJ7" s="5" t="inlineStr">
         <is>
-          <t>Julio 2026</t>
+          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AK7" s="5" t="inlineStr">
         <is>
-          <t>Agosto 2026</t>
+          <t>Septiembre 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -1052,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="7" t="n">
         <v>0</v>
@@ -1142,16 +1149,16 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -1205,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="7" t="n">
         <v>0</v>
@@ -1220,10 +1227,10 @@
         <v>0</v>
       </c>
       <c r="AB10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" s="7" t="n">
         <v>0</v>
@@ -1250,11 +1257,11 @@
         <v>0</v>
       </c>
       <c r="AL10" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 4; fotodetección previa: 0. Sensibilidad: todo estricto 2; todo +15 m 4.</t>
+          <t>Agentes: 3; fotodetección previa: 0. Sensibilidad: todo estricto 1; todo +15 m 3.</t>
         </is>
       </c>
     </row>
@@ -1388,16 +1395,16 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -1421,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
         <v>0</v>
@@ -1439,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="7" t="n">
         <v>0</v>
@@ -1568,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="U13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="7" t="n">
         <v>0</v>
@@ -1580,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z13" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="7" t="n">
         <v>0</v>
@@ -1634,16 +1641,16 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
@@ -1703,10 +1710,10 @@
         <v>0</v>
       </c>
       <c r="Y14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="7" t="n">
         <v>0</v>
@@ -1742,11 +1749,11 @@
         <v>0</v>
       </c>
       <c r="AL14" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 8; fotodetección previa: 0. Sensibilidad: todo estricto 8; todo +15 m 9.</t>
+          <t>Agentes: 5; fotodetección previa: 0. Sensibilidad: todo estricto 5; todo +15 m 6.</t>
         </is>
       </c>
     </row>
@@ -1757,119 +1764,119 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="X15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="8" t="n">
-        <v>8</v>
-      </c>
       <c r="AM15" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 8; fotodetección previa: 0. Sensibilidad: todo estricto 7; todo +15 m 8.</t>
+          <t>Agentes: 4; fotodetección previa: 0. Sensibilidad: todo estricto 3; todo +15 m 4.</t>
         </is>
       </c>
     </row>
@@ -2159,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18" s="7" t="n">
         <v>0</v>
@@ -3124,7 +3131,7 @@
         </is>
       </c>
       <c r="E25" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="10" t="n"/>
       <c r="G25" s="10" t="n"/>
@@ -3132,7 +3139,7 @@
         <v>2</v>
       </c>
       <c r="I25" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -3155,19 +3162,19 @@
         </is>
       </c>
       <c r="E26" s="10" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="H26" s="10" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="I26" s="10" t="n">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="27">
@@ -3295,19 +3302,19 @@
         </is>
       </c>
       <c r="E30" s="10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F30" s="10" t="n">
         <v>3</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H30" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I30" s="10" t="n">
         <v>16</v>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -3330,19 +3337,19 @@
         </is>
       </c>
       <c r="E31" s="10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F31" s="10" t="n">
         <v>6</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H31" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="I31" s="10" t="n">
         <v>20</v>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="32">
@@ -3466,15 +3473,15 @@
         </is>
       </c>
       <c r="E35" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" s="10" t="n"/>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -3497,19 +3504,19 @@
         </is>
       </c>
       <c r="E36" s="10" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F36" s="10" t="n">
         <v>43</v>
       </c>
       <c r="G36" s="10" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H36" s="10" t="n">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I36" s="10" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37">
@@ -3567,19 +3574,19 @@
         </is>
       </c>
       <c r="E38" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H38" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -3637,19 +3644,19 @@
         </is>
       </c>
       <c r="E40" s="10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H40" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I40" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -3672,19 +3679,19 @@
         </is>
       </c>
       <c r="E41" s="10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F41" s="10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G41" s="10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H41" s="10" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I41" s="10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
@@ -3808,7 +3815,7 @@
         </is>
       </c>
       <c r="E45" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" s="10" t="n"/>
       <c r="G45" s="10" t="n"/>
@@ -3816,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="I45" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3839,19 +3846,19 @@
         </is>
       </c>
       <c r="E46" s="10" t="n">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="H46" s="10" t="n">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="I46" s="10" t="n">
-        <v>1304</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="47">
@@ -3921,7 +3928,7 @@
         <v>14</v>
       </c>
       <c r="I48" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -3944,19 +3951,19 @@
         </is>
       </c>
       <c r="E49" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F49" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G49" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I49" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50">
@@ -3979,19 +3986,19 @@
         </is>
       </c>
       <c r="E50" s="10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F50" s="10" t="n">
         <v>5</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H50" s="10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I50" s="10" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51">
@@ -4014,16 +4021,16 @@
         </is>
       </c>
       <c r="E51" s="10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F51" s="10" t="n">
         <v>8</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H51" s="10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I51" s="10" t="n">
         <v>85</v>
@@ -4049,19 +4056,19 @@
         </is>
       </c>
       <c r="E52" s="10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G52" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="10" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I52" s="10" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53">
@@ -4084,19 +4091,19 @@
         </is>
       </c>
       <c r="E53" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="F53" s="10" t="n">
-        <v>12</v>
-      </c>
-      <c r="G53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>11</v>
-      </c>
       <c r="I53" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
@@ -4181,19 +4188,19 @@
         </is>
       </c>
       <c r="E56" s="10" t="n">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>374</v>
+        <v>493</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>871</v>
+        <v>849</v>
       </c>
       <c r="H56" s="10" t="n">
-        <v>1232</v>
+        <v>1327</v>
       </c>
       <c r="I56" s="10" t="n">
-        <v>1350</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="57">
@@ -4216,19 +4223,19 @@
         </is>
       </c>
       <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F57" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G57" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I57" s="10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -4251,19 +4258,19 @@
         </is>
       </c>
       <c r="E58" s="10" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="10" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="I58" s="10" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59">
@@ -4286,19 +4293,19 @@
         </is>
       </c>
       <c r="E59" s="10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F59" s="10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G59" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I59" s="10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="60">
@@ -4321,19 +4328,19 @@
         </is>
       </c>
       <c r="E60" s="10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H60" s="10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" s="10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61">
@@ -4356,19 +4363,19 @@
         </is>
       </c>
       <c r="E61" s="10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F61" s="10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G61" s="10" t="n">
         <v>61</v>
       </c>
       <c r="H61" s="10" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I61" s="10" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62">
@@ -4391,19 +4398,19 @@
         </is>
       </c>
       <c r="E62" s="10" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="G62" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="10" t="n">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I62" s="10" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
     </row>
     <row r="63">
@@ -4426,19 +4433,19 @@
         </is>
       </c>
       <c r="E63" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F63" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I63" s="10" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
@@ -4523,19 +4530,19 @@
         </is>
       </c>
       <c r="E66" s="10" t="n">
-        <v>2251</v>
+        <v>2233</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>1995</v>
+        <v>1973</v>
       </c>
       <c r="H66" s="10" t="n">
-        <v>2230</v>
+        <v>2212</v>
       </c>
       <c r="I66" s="10" t="n">
-        <v>2421</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="67">
@@ -4628,19 +4635,19 @@
         </is>
       </c>
       <c r="E69" s="10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F69" s="10" t="n">
         <v>5</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H69" s="10" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I69" s="10" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="70">
@@ -4663,19 +4670,19 @@
         </is>
       </c>
       <c r="E70" s="10" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F70" s="10" t="n">
         <v>12</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H70" s="10" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I70" s="10" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="71">
@@ -4865,19 +4872,19 @@
         </is>
       </c>
       <c r="E76" s="10" t="n">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>1300</v>
+        <v>1275</v>
       </c>
       <c r="H76" s="10" t="n">
-        <v>1603</v>
+        <v>1589</v>
       </c>
       <c r="I76" s="10" t="n">
-        <v>1780</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="77">
@@ -5207,19 +5214,19 @@
         </is>
       </c>
       <c r="E86" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H86" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87">
@@ -5347,19 +5354,19 @@
         </is>
       </c>
       <c r="E90" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G90" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H90" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I90" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -5382,19 +5389,19 @@
         </is>
       </c>
       <c r="E91" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F91" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="H91" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I91" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -5595,13 +5602,13 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="C4" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="C4" s="10" t="n">
-        <v>41</v>
-      </c>
       <c r="D4" s="10" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>11</v>
@@ -5614,16 +5621,16 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6">
@@ -5633,16 +5640,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>671</v>
+        <v>703</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>275</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7">
@@ -5652,16 +5659,16 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>547</v>
+        <v>684</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>486</v>
+        <v>617</v>
       </c>
       <c r="D7" s="10" t="n">
+        <v>473</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>360</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>268</v>
       </c>
     </row>
     <row r="8">
@@ -5671,16 +5678,16 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9">
@@ -5690,16 +5697,16 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -5709,16 +5716,16 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -5732,7 +5739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5981,14 +5988,14 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Con Heridos</t>
+          <t>Con Muertos</t>
         </is>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
@@ -6000,11 +6007,7 @@
           <t xml:space="preserve">CARRERA 12 CON CALLE 21 LA GRANJA </t>
         </is>
       </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>20001_2025_DECESO CLINICO CLINICO 7 (Deceso clínico, 01/06/2025, m 1 h 0)</t>
-        </is>
-      </c>
+      <c r="I6" s="10" t="n"/>
       <c r="J6" s="10" t="b">
         <v>1</v>
       </c>
@@ -6012,45 +6015,41 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>EQUIPO031, EQUIPO032</t>
+          <t>EQUIPO051</t>
         </is>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>20001_2025_DECESO CLINICO CLINICO 7</t>
+          <t>20001_1396923</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>Con Muertos</t>
+          <t>Con Heridos</t>
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Deceso clínico</t>
+          <t>Reporte Siniestro STTV</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>CARRERA 12 CON CALLE 21 BARRIO LA GRANJA</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>20001_1396898 (Reporte Siniestro STTV, 01/06/2025, m 0 h 2)</t>
-        </is>
-      </c>
+          <t>CARRERA 9 CON CALLE 18</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n"/>
       <c r="J7" s="10" t="b">
         <v>1</v>
       </c>
@@ -6058,17 +6057,17 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>EQUIPO051</t>
+          <t>EQUIPO032</t>
         </is>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>20001_1396923</t>
+          <t>{E839B981-10B1-45CF-892A-EC61609E3BB2}</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
@@ -6080,7 +6079,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
@@ -6089,10 +6088,14 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>CARRERA 9 CON CALLE 18</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="n"/>
+          <t>Calle 22 con carrera 16 B/Simón Bolívar Av Pastrana</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>{85BEC3D3-DBE7-4272-8B8E-6588D599D0B2} (Reporte Siniestro STTV, 27/06/2026, m 0 h 2)</t>
+        </is>
+      </c>
       <c r="J8" s="10" t="b">
         <v>1</v>
       </c>
@@ -6100,17 +6103,17 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>EQUIPO032</t>
+          <t>EQUIPO031, EQUIPO032</t>
         </is>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>{E839B981-10B1-45CF-892A-EC61609E3BB2}</t>
+          <t>{85BEC3D3-DBE7-4272-8B8E-6588D599D0B2}</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="D9" s="10" t="inlineStr">
@@ -6122,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
@@ -6131,12 +6134,12 @@
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Calle 22 con carrera 16 B/Simón Bolívar Av Pastrana</t>
+          <t>Calle 21 con carrera 16</t>
         </is>
       </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
-          <t>{85BEC3D3-DBE7-4272-8B8E-6588D599D0B2} (Reporte Siniestro STTV, 27/06/2026, m 0 h 2)</t>
+          <t>{E839B981-10B1-45CF-892A-EC61609E3BB2} (Reporte Siniestro STTV, 26/06/2026, m 0 h 1)</t>
         </is>
       </c>
       <c r="J9" s="10" t="b">
@@ -6146,17 +6149,17 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>EQUIPO031, EQUIPO032</t>
+          <t>EQUIPO032</t>
         </is>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>{85BEC3D3-DBE7-4272-8B8E-6588D599D0B2}</t>
+          <t>{80D3CB19-1C2B-4E62-8613-E344CC2F7E3C}</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
@@ -6168,7 +6171,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
@@ -6177,14 +6180,10 @@
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Calle 21 con carrera 16</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>{E839B981-10B1-45CF-892A-EC61609E3BB2} (Reporte Siniestro STTV, 26/06/2026, m 0 h 1)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Calle 22 con carrera 16 </t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="n"/>
       <c r="J10" s="10" t="b">
         <v>1</v>
       </c>
@@ -6192,17 +6191,17 @@
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>EQUIPO032</t>
+          <t>EQUIPO041</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>{80D3CB19-1C2B-4E62-8613-E344CC2F7E3C}</t>
+          <t>{1881E171-3ED8-42F7-8F6A-AEB92C9CD206}</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D11" s="10" t="inlineStr">
@@ -6223,54 +6222,12 @@
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Calle 22 con carrera 16 </t>
+          <t>Diagonal 16 con 16 - 46</t>
         </is>
       </c>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>EQUIPO041</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>{1881E171-3ED8-42F7-8F6A-AEB92C9CD206}</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>Con Heridos</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Reporte Siniestro STTV</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Diagonal 16 con 16 - 46</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6401,22 +6358,22 @@
         </is>
       </c>
       <c r="B3" s="10" t="n">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C3" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E3" s="10" t="n">
         <v>3</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H3" s="10" t="n">
         <v>4</v>
@@ -6428,7 +6385,7 @@
         <v>3</v>
       </c>
       <c r="K3" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -6438,34 +6395,34 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>1422</v>
+        <v>1540</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F4" s="10" t="n">
         <v>84</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="I4" s="10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="K4" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -6475,7 +6432,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>3028</v>
+        <v>3008</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>2</v>
@@ -6487,10 +6444,10 @@
         <v>13</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>11</v>
@@ -6512,7 +6469,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>0</v>
@@ -6524,10 +6481,10 @@
         <v>3</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H6" s="10" t="n">
         <v>0</v>
@@ -11656,7 +11613,7 @@
         <v>0</v>
       </c>
       <c r="AW32" s="10" t="n">
-        <v>1268</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33">
@@ -15486,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="AH57" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI57" s="10" t="n">
         <v>0</v>
@@ -18431,7 +18388,7 @@
         <v>0</v>
       </c>
       <c r="AH76" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="10" t="n">
         <v>0</v>
@@ -21731,7 +21688,7 @@
         <v>0</v>
       </c>
       <c r="AW97" s="10" t="n">
-        <v>815</v>
+        <v>443</v>
       </c>
     </row>
     <row r="98">
@@ -22658,10 +22615,10 @@
         <v>0</v>
       </c>
       <c r="AV103" s="10" t="n">
-        <v>1343</v>
+        <v>470</v>
       </c>
       <c r="AW103" s="10" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104">
@@ -26381,7 +26338,7 @@
         <v>0</v>
       </c>
       <c r="AW127" s="10" t="n">
-        <v>815</v>
+        <v>372</v>
       </c>
     </row>
     <row r="128">
@@ -27153,10 +27110,10 @@
         <v>0</v>
       </c>
       <c r="AV132" s="10" t="n">
-        <v>1343</v>
+        <v>873</v>
       </c>
       <c r="AW132" s="10" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="133">
@@ -33666,7 +33623,7 @@
         <v>0</v>
       </c>
       <c r="AW174" s="10" t="n">
-        <v>992</v>
+        <v>475</v>
       </c>
     </row>
     <row r="175">
@@ -34286,7 +34243,7 @@
         <v>0</v>
       </c>
       <c r="AW178" s="10" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179">
@@ -36318,7 +36275,7 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
     <col width="9" customWidth="1" min="4" max="4"/>
@@ -36327,7 +36284,7 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>equipo_zona</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">
@@ -36379,7 +36336,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="10" t="n">
-        <v>1268</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4">
@@ -36469,7 +36426,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>815</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -36484,10 +36441,10 @@
         </is>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1343</v>
+        <v>470</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -36505,7 +36462,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>815</v>
+        <v>372</v>
       </c>
     </row>
     <row r="11">
@@ -36520,10 +36477,10 @@
         </is>
       </c>
       <c r="C11" s="10" t="n">
-        <v>1343</v>
+        <v>873</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12">
@@ -36577,7 +36534,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>992</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15">
@@ -36595,7 +36552,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -36804,7 +36761,7 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>direccion</t>
+          <t>equipo</t>
         </is>
       </c>
       <c r="C8" s="10" t="n">
@@ -37421,16 +37378,16 @@
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B31" s="10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="10" t="n">
         <v>6</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
@@ -37794,7 +37751,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 02/09/2026    Código único: CU000000000908    Solicitud: SOL0000010402    Dirección ANSV: DIAGONAL 21 - CARRERA 19 (SENTIDO SUR - NORTE)</t>
         </is>
       </c>
     </row>
@@ -39453,7 +39410,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 02/09/2026    Código único: CU000000000909    Solicitud: SOL0000010402    Dirección ANSV: DIAGONAL 21 - CARRERA 18E (SENTIDO NORTE - SUR)</t>
         </is>
       </c>
     </row>
@@ -41112,7 +41069,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 27/08/2026    Código único: CU000000000907    Solicitud: SOL0000010802    Dirección ANSV: CALLE 21 - CARRERA 15 (SENTIDO OESTE - ESTE)</t>
         </is>
       </c>
     </row>
@@ -41153,182 +41110,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Agosto 2023</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>Septiembre 2023</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2023</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2023</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2023</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Enero 2024</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2024</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2024</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Abril 2024</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2024</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Junio 2024</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Julio 2024</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2024</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2024</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2024</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2024</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2024</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Enero 2025</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2025</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2025</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Abril 2025</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2025</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Junio 2025</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Julio 2025</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2025</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2025</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2025</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2025</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2025</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>Enero 2026</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2026</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2026</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>Abril 2026</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>Junio 2026</t>
         </is>
       </c>
-      <c r="AJ7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Julio 2026</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -41361,10 +41318,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>0</v>
@@ -41412,10 +41369,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="7" t="n">
         <v>0</v>
@@ -41535,52 +41492,52 @@
         <v>0</v>
       </c>
       <c r="W9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="X9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ9" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AK9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM9" s="9" t="inlineStr">
         <is>
@@ -41595,7 +41552,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -41610,13 +41567,13 @@
         <v>0</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J10" s="7" t="n">
         <v>6</v>
@@ -41628,86 +41585,86 @@
         <v>6</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="O10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="T10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="V10" s="7" t="n">
+      <c r="W10" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="X10" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="Y10" s="7" t="n">
         <v>23</v>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="AA10" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="AA10" s="7" t="n">
+      <c r="AB10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AB10" s="7" t="n">
+      <c r="AC10" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="AC10" s="7" t="n">
+      <c r="AD10" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="AD10" s="7" t="n">
+      <c r="AE10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AE10" s="7" t="n">
+      <c r="AF10" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="AF10" s="7" t="n">
+      <c r="AG10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="AG10" s="7" t="n">
+      <c r="AH10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AI10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AI10" s="7" t="n">
+      <c r="AJ10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AJ10" s="7" t="n">
+      <c r="AK10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AK10" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="AL10" s="8" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 21; fotodetección previa: 300. Sensibilidad: todo estricto 316; todo +15 m 330.</t>
+          <t>Agentes: 22; fotodetección previa: 295. Sensibilidad: todo estricto 312; todo +15 m 326.</t>
         </is>
       </c>
     </row>
@@ -41859,14 +41816,14 @@
         <v>0</v>
       </c>
       <c r="H12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="J12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="J12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" s="7" t="n">
         <v>0</v>
       </c>
@@ -41877,11 +41834,11 @@
         <v>0</v>
       </c>
       <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" s="7" t="n">
         <v>0</v>
       </c>
@@ -41916,10 +41873,10 @@
         <v>0</v>
       </c>
       <c r="AA12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" s="7" t="n">
         <v>0</v>
@@ -41928,10 +41885,10 @@
         <v>0</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="7" t="n">
         <v>0</v>
@@ -41994,11 +41951,11 @@
         <v>0</v>
       </c>
       <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
@@ -42024,10 +41981,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
@@ -42108,11 +42065,11 @@
         <v>0</v>
       </c>
       <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" s="7" t="n">
         <v>0</v>
       </c>
@@ -42129,49 +42086,49 @@
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="T14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="U14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="V14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AC14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AD14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="7" t="n">
         <v>0</v>
@@ -42180,10 +42137,10 @@
         <v>0</v>
       </c>
       <c r="AG14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="7" t="n">
         <v>0</v>
@@ -42192,14 +42149,14 @@
         <v>0</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 3; fotodetección previa: 13. Sensibilidad: todo estricto 16; todo +15 m 17.</t>
+          <t>Agentes: 3; fotodetección previa: 12. Sensibilidad: todo estricto 15; todo +15 m 16.</t>
         </is>
       </c>
     </row>
@@ -42228,58 +42185,58 @@
         <v>0</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="R15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="W15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="7" t="n">
         <v>1</v>
@@ -42288,41 +42245,41 @@
         <v>1</v>
       </c>
       <c r="AB15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AC15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" s="8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM15" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 6; fotodetección previa: 14. Sensibilidad: todo estricto 20; todo +15 m 21.</t>
+          <t>Agentes: 6; fotodetección previa: 13. Sensibilidad: todo estricto 19; todo +15 m 20.</t>
         </is>
       </c>
     </row>
@@ -42333,10 +42290,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>0</v>
@@ -42360,19 +42317,19 @@
         <v>0</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16" s="7" t="n">
         <v>0</v>
@@ -42486,10 +42443,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
         <v>0</v>
@@ -42648,7 +42605,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 27/08/2026    Código único: CU000000000906    Solicitud: SOL0000010802    Dirección ANSV: TRANSVERSAL 12 - CALLE 20B (SENTIDO NORTE - SUR)</t>
         </is>
       </c>
     </row>
@@ -42689,182 +42646,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Agosto 2023</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>Septiembre 2023</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2023</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2023</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2023</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Enero 2024</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2024</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2024</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Abril 2024</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2024</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Junio 2024</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Julio 2024</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2024</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2024</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2024</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2024</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2024</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Enero 2025</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2025</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2025</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Abril 2025</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2025</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Junio 2025</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Julio 2025</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2025</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2025</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2025</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2025</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2025</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>Enero 2026</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2026</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2026</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>Abril 2026</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>Junio 2026</t>
         </is>
       </c>
-      <c r="AJ7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Julio 2026</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -42897,10 +42854,10 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="n">
         <v>0</v>
@@ -42933,10 +42890,10 @@
         <v>0</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" s="7" t="n">
         <v>0</v>
@@ -42948,10 +42905,10 @@
         <v>0</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" s="7" t="n">
         <v>0</v>
@@ -43071,10 +43028,10 @@
         <v>0</v>
       </c>
       <c r="W9" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" s="7" t="n">
         <v>0</v>
@@ -43107,20 +43064,20 @@
         <v>0</v>
       </c>
       <c r="AI9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AJ9" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AK9" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM9" s="9" t="inlineStr">
         <is>
-          <t>Portal ANSV (personas), corte 2026-10-06. Sensibilidad: polígono estricto 4. SALVEDAD: el portal registra muchos menos lesionados por mes en 2023–2025 que en 2026 (cambio de captura, hoja «Cobertura portal»); la serie no es homogénea y el valor puede estar subestimado.</t>
+          <t>Portal ANSV (personas), corte 2026-10-06. Sensibilidad: polígono estricto 3. SALVEDAD: el portal registra muchos menos lesionados por mes en 2023–2025 que en 2026 (cambio de captura, hoja «Cobertura portal»); la serie no es homogénea y el valor puede estar subestimado.</t>
         </is>
       </c>
     </row>
@@ -43131,119 +43088,119 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="O10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="P10" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="T10" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="V10" s="7" t="n">
+      <c r="W10" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="X10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="Y10" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="AA10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="AA10" s="7" t="n">
+      <c r="AB10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AB10" s="7" t="n">
+      <c r="AC10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="AC10" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AD10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AE10" s="7" t="n">
+      <c r="AF10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AF10" s="7" t="n">
+      <c r="AG10" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AG10" s="7" t="n">
+      <c r="AH10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AI10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AI10" s="7" t="n">
+      <c r="AJ10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AJ10" s="7" t="n">
+      <c r="AK10" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AK10" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="AL10" s="8" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 43; fotodetección previa: 258. Sensibilidad: todo estricto 297; todo +15 m 356.</t>
+          <t>Agentes: 43; fotodetección previa: 256. Sensibilidad: todo estricto 296; todo +15 m 357.</t>
         </is>
       </c>
     </row>
@@ -43377,7 +43334,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -43398,10 +43355,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>0</v>
@@ -43413,10 +43370,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="7" t="n">
         <v>0</v>
@@ -43464,10 +43421,10 @@
         <v>0</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="7" t="n">
         <v>0</v>
@@ -43485,11 +43442,11 @@
         <v>0</v>
       </c>
       <c r="AL12" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM12" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 3; fotodetección previa: 0. Sensibilidad: todo estricto 1; todo +15 m 4.</t>
+          <t>Agentes: 4; fotodetección previa: 0. Sensibilidad: todo estricto 2; todo +15 m 5.</t>
         </is>
       </c>
     </row>
@@ -43530,11 +43487,11 @@
         <v>0</v>
       </c>
       <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
@@ -43560,10 +43517,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
@@ -43623,7 +43580,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -43650,11 +43607,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="7" t="n">
         <v>0</v>
       </c>
@@ -43665,28 +43622,28 @@
         <v>0</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="R14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="S14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="U14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" s="7" t="n">
         <v>0</v>
@@ -43701,10 +43658,10 @@
         <v>0</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD14" s="7" t="n">
         <v>0</v>
@@ -43716,10 +43673,10 @@
         <v>0</v>
       </c>
       <c r="AG14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" s="7" t="n">
         <v>0</v>
@@ -43728,14 +43685,14 @@
         <v>0</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 2; fotodetección previa: 13. Sensibilidad: todo estricto 14; todo +15 m 20.</t>
+          <t>Agentes: 8; fotodetección previa: 12. Sensibilidad: todo estricto 18; todo +15 m 25.</t>
         </is>
       </c>
     </row>
@@ -43746,7 +43703,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -43770,46 +43727,46 @@
         <v>0</v>
       </c>
       <c r="J15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K15" s="7" t="n">
+      <c r="L15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="7" t="n">
         <v>2</v>
       </c>
       <c r="R15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="S15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="T15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" s="7" t="n">
         <v>0</v>
@@ -43818,22 +43775,22 @@
         <v>0</v>
       </c>
       <c r="Z15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" s="7" t="n">
         <v>0</v>
@@ -43851,14 +43808,14 @@
         <v>0</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" s="8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AM15" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 3; fotodetección previa: 17. Sensibilidad: todo estricto 19; todo +15 m 20.</t>
+          <t>Agentes: 9; fotodetección previa: 16. Sensibilidad: todo estricto 24; todo +15 m 26.</t>
         </is>
       </c>
     </row>
@@ -43869,10 +43826,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>0</v>
@@ -44016,16 +43973,16 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
         <v>0</v>
@@ -44184,7 +44141,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 18/08/2026    Código único: CU000000000915    Solicitud: SOL0000010743    Dirección ANSV: CALLE 16 - CARRERA 12 (OESTE - ESTE)</t>
         </is>
       </c>
     </row>
@@ -44225,182 +44182,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Agosto 2023</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>Septiembre 2023</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2023</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2023</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2023</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Enero 2024</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2024</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2024</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Abril 2024</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2024</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Junio 2024</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Julio 2024</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2024</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2024</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2024</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2024</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2024</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Enero 2025</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2025</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2025</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Abril 2025</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2025</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Junio 2025</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Julio 2025</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2025</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2025</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2025</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2025</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2025</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>Enero 2026</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2026</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2026</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>Abril 2026</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>Junio 2026</t>
         </is>
       </c>
-      <c r="AJ7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Julio 2026</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -44649,10 +44606,10 @@
         <v>0</v>
       </c>
       <c r="AK9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL9" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM9" s="9" t="inlineStr">
         <is>
@@ -44667,119 +44624,119 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="D10" s="7" t="n">
         <v>34</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>5</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="I10" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="O10" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="P10" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="T10" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="V10" s="7" t="n">
+      <c r="W10" s="7" t="n">
         <v>25</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="X10" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="Y10" s="7" t="n">
         <v>21</v>
-      </c>
-      <c r="Y10" s="7" t="n">
-        <v>13</v>
       </c>
       <c r="Z10" s="7" t="n">
         <v>13</v>
       </c>
       <c r="AA10" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB10" s="7" t="n">
         <v>18</v>
-      </c>
-      <c r="AB10" s="7" t="n">
-        <v>8</v>
       </c>
       <c r="AC10" s="7" t="n">
         <v>8</v>
       </c>
       <c r="AD10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="AE10" s="7" t="n">
+      <c r="AF10" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AF10" s="7" t="n">
+      <c r="AG10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AG10" s="7" t="n">
+      <c r="AH10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AI10" s="7" t="n">
         <v>6</v>
-      </c>
-      <c r="AI10" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="AJ10" s="7" t="n">
         <v>4</v>
       </c>
       <c r="AK10" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL10" s="8" t="n">
-        <v>573</v>
+        <v>586</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 206; fotodetección previa: 367. Sensibilidad: todo estricto 533; todo +15 m 1304.</t>
+          <t>Agentes: 221; fotodetección previa: 365. Sensibilidad: todo estricto 546; todo +15 m 1331.</t>
         </is>
       </c>
     </row>
@@ -44913,10 +44870,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
@@ -44937,22 +44894,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7" t="n">
         <v>11</v>
       </c>
-      <c r="K12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="7" t="n">
         <v>0</v>
@@ -44994,10 +44951,10 @@
         <v>0</v>
       </c>
       <c r="AC12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" s="7" t="n">
         <v>0</v>
@@ -45015,17 +44972,17 @@
         <v>0</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" s="8" t="n">
         <v>16</v>
       </c>
       <c r="AM12" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 16; fotodetección previa: 0. Sensibilidad: todo estricto 14; todo +15 m 21.</t>
+          <t>Agentes: 16; fotodetección previa: 0. Sensibilidad: todo estricto 14; todo +15 m 20.</t>
         </is>
       </c>
     </row>
@@ -45036,7 +44993,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -45063,14 +45020,14 @@
         <v>0</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" s="7" t="n">
         <v>0</v>
       </c>
@@ -45078,14 +45035,14 @@
         <v>0</v>
       </c>
       <c r="P13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="R13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="S13" s="7" t="n">
         <v>0</v>
       </c>
@@ -45096,10 +45053,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="7" t="n">
         <v>0</v>
@@ -45123,11 +45080,11 @@
         <v>0</v>
       </c>
       <c r="AE13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG13" s="7" t="n">
         <v>0</v>
       </c>
@@ -45144,11 +45101,11 @@
         <v>0</v>
       </c>
       <c r="AL13" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AM13" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 11; fotodetección previa: 0. Sensibilidad: todo estricto 11; todo +15 m 14.</t>
+          <t>Agentes: 13; fotodetección previa: 0. Sensibilidad: todo estricto 13; todo +15 m 16.</t>
         </is>
       </c>
     </row>
@@ -45177,77 +45134,77 @@
         <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="J14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="P14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="Q14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="S14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="T14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="U14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="V14" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="X14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Z14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AE14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AE14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AF14" s="7" t="n">
         <v>0</v>
       </c>
@@ -45255,23 +45212,23 @@
         <v>0</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="8" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 5; fotodetección previa: 29. Sensibilidad: todo estricto 33; todo +15 m 78.</t>
+          <t>Agentes: 5; fotodetección previa: 28. Sensibilidad: todo estricto 32; todo +15 m 74.</t>
         </is>
       </c>
     </row>
@@ -45300,7 +45257,7 @@
         <v>0</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>1</v>
@@ -45309,34 +45266,34 @@
         <v>1</v>
       </c>
       <c r="K15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L15" s="7" t="n">
+      <c r="M15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="P15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="Q15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="S15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15" s="7" t="n">
         <v>1</v>
@@ -45351,26 +45308,26 @@
         <v>1</v>
       </c>
       <c r="Y15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Z15" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AA15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AC15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AE15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AF15" s="7" t="n">
         <v>0</v>
       </c>
@@ -45387,14 +45344,14 @@
         <v>0</v>
       </c>
       <c r="AK15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL15" s="8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM15" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 8; fotodetección previa: 21. Sensibilidad: todo estricto 26; todo +15 m 85.</t>
+          <t>Agentes: 8; fotodetección previa: 20. Sensibilidad: todo estricto 25; todo +15 m 85.</t>
         </is>
       </c>
     </row>
@@ -45405,7 +45362,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -45426,46 +45383,46 @@
         <v>0</v>
       </c>
       <c r="I16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="K16" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="L16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="O16" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="P16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="V16" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W16" s="7" t="n">
         <v>0</v>
@@ -45486,10 +45443,10 @@
         <v>0</v>
       </c>
       <c r="AC16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16" s="7" t="n">
         <v>0</v>
@@ -45498,14 +45455,14 @@
         <v>0</v>
       </c>
       <c r="AG16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AI16" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ16" s="7" t="n">
         <v>0</v>
       </c>
@@ -45513,11 +45470,11 @@
         <v>0</v>
       </c>
       <c r="AL16" s="8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AM16" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 82; fotodetección previa: 0. Sensibilidad: todo estricto 81; todo +15 m 89.</t>
+          <t>Agentes: 84; fotodetección previa: 0. Sensibilidad: todo estricto 83; todo +15 m 91.</t>
         </is>
       </c>
     </row>
@@ -45528,7 +45485,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>0</v>
@@ -45552,11 +45509,11 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" s="7" t="n">
         <v>0</v>
       </c>
@@ -45564,10 +45521,10 @@
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" s="7" t="n">
         <v>0</v>
@@ -45603,10 +45560,10 @@
         <v>0</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="7" t="n">
         <v>0</v>
@@ -45624,10 +45581,10 @@
         <v>0</v>
       </c>
       <c r="AH17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" s="7" t="n">
         <v>0</v>
@@ -45636,11 +45593,11 @@
         <v>0</v>
       </c>
       <c r="AL17" s="8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM17" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 12; fotodetección previa: 0. Sensibilidad: todo estricto 11; todo +15 m 14.</t>
+          <t>Agentes: 13; fotodetección previa: 0. Sensibilidad: todo estricto 12; todo +15 m 16.</t>
         </is>
       </c>
     </row>
@@ -45720,7 +45677,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 17/06/2026    Código único: CU000000000914    Solicitud: SOL0000010743    Dirección ANSV: CARRERA 12 - CALLE 16 (SUR - NORTE)</t>
         </is>
       </c>
     </row>
@@ -45761,182 +45718,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Junio 2023</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Julio 2023</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Agosto 2023</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
           <t>Septiembre 2023</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2023</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2023</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2023</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Enero 2024</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2024</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2024</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Abril 2024</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2024</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Junio 2024</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Julio 2024</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2024</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2024</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2024</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2024</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2024</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Enero 2025</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2025</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2025</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Abril 2025</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2025</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>Junio 2025</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>Julio 2025</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2025</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2025</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2025</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2025</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2025</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>Enero 2026</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2026</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2026</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>Abril 2026</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
-        </is>
-      </c>
-      <c r="AI7" s="5" t="inlineStr">
-        <is>
-          <t>Junio 2026</t>
-        </is>
-      </c>
-      <c r="AJ7" s="5" t="inlineStr">
-        <is>
-          <t>Julio 2026</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -46203,119 +46160,119 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
+        <v>49</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="E10" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="I10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="K10" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>73</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="O10" s="7" t="n">
         <v>71</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="P10" s="7" t="n">
         <v>33</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="Q10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="S10" s="7" t="n">
         <v>21</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="T10" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>67</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="W10" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="X10" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="V10" s="7" t="n">
+      <c r="Y10" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="AA10" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="AB10" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="AC10" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="AA10" s="7" t="n">
+      <c r="AD10" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="AB10" s="7" t="n">
+      <c r="AE10" s="7" t="n">
         <v>23</v>
-      </c>
-      <c r="AC10" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD10" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE10" s="7" t="n">
-        <v>11</v>
       </c>
       <c r="AF10" s="7" t="n">
         <v>11</v>
       </c>
       <c r="AG10" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH10" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI10" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AK10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="AI10" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ10" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AK10" s="7" t="n">
-        <v>5</v>
-      </c>
       <c r="AL10" s="8" t="n">
-        <v>1245</v>
+        <v>1342</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 374; fotodetección previa: 871. Sensibilidad: todo estricto 1232; todo +15 m 1350.</t>
+          <t>Agentes: 493; fotodetección previa: 849. Sensibilidad: todo estricto 1327; todo +15 m 1451.</t>
         </is>
       </c>
     </row>
@@ -46326,7 +46283,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -46434,11 +46391,11 @@
         <v>0</v>
       </c>
       <c r="AL11" s="8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AM11" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 0; fotodetección previa: 0. Sensibilidad: todo estricto 0; todo +15 m 0.</t>
+          <t>Agentes: 5; fotodetección previa: 0. Sensibilidad: todo estricto 5; todo +15 m 5.</t>
         </is>
       </c>
     </row>
@@ -46449,19 +46406,19 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="F12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -46473,22 +46430,22 @@
         <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="K12" s="7" t="n">
+      <c r="N12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="L12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="O12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="7" t="n">
         <v>0</v>
@@ -46503,40 +46460,40 @@
         <v>0</v>
       </c>
       <c r="T12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="U12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" s="7" t="n">
+      <c r="X12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="W12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Z12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" s="7" t="n">
         <v>0</v>
@@ -46545,7 +46502,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="7" t="n">
         <v>0</v>
@@ -46554,14 +46511,14 @@
         <v>0</v>
       </c>
       <c r="AK12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL12" s="8" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM12" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 36; fotodetección previa: 0. Sensibilidad: todo estricto 33; todo +15 m 47.</t>
+          <t>Agentes: 46; fotodetección previa: 0. Sensibilidad: todo estricto 42; todo +15 m 60.</t>
         </is>
       </c>
     </row>
@@ -46575,10 +46532,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E13" s="7" t="n">
         <v>0</v>
@@ -46599,22 +46556,22 @@
         <v>0</v>
       </c>
       <c r="K13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="O13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="7" t="n">
         <v>1</v>
@@ -46623,16 +46580,16 @@
         <v>0</v>
       </c>
       <c r="S13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="7" t="n">
         <v>0</v>
@@ -46641,7 +46598,7 @@
         <v>0</v>
       </c>
       <c r="Y13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z13" s="7" t="n">
         <v>0</v>
@@ -46659,17 +46616,17 @@
         <v>0</v>
       </c>
       <c r="AE13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AI13" s="7" t="n">
         <v>0</v>
       </c>
@@ -46680,11 +46637,11 @@
         <v>0</v>
       </c>
       <c r="AL13" s="8" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AM13" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 12; fotodetección previa: 0. Sensibilidad: todo estricto 12; todo +15 m 12.</t>
+          <t>Agentes: 17; fotodetección previa: 0. Sensibilidad: todo estricto 17; todo +15 m 17.</t>
         </is>
       </c>
     </row>
@@ -46698,13 +46655,13 @@
         <v>1</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
@@ -46713,101 +46670,101 @@
         <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7" t="n">
+      <c r="L14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="O14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="7" t="n">
+      <c r="T14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="R14" s="7" t="n">
+      <c r="U14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="S14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T14" s="7" t="n">
+      <c r="V14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" s="7" t="n">
         <v>8</v>
-      </c>
-      <c r="U14" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="V14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="W14" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="X14" s="7" t="n">
         <v>5</v>
       </c>
       <c r="Y14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA14" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="Z14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AC14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AD14" s="7" t="n">
+      <c r="AG14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AE14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AH14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AI14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AL14" s="8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 12; fotodetección previa: 62. Sensibilidad: todo estricto 72; todo +15 m 81.</t>
+          <t>Agentes: 14; fotodetección previa: 61. Sensibilidad: todo estricto 73; todo +15 m 82.</t>
         </is>
       </c>
     </row>
@@ -46818,101 +46775,101 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" s="7" t="n">
         <v>8</v>
       </c>
       <c r="L15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="M15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" s="7" t="n">
+      <c r="P15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" s="7" t="n">
+      <c r="R15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Q15" s="7" t="n">
+      <c r="T15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="S15" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" s="7" t="n">
-        <v>7</v>
       </c>
       <c r="U15" s="7" t="n">
         <v>5</v>
       </c>
       <c r="V15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="X15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="W15" s="7" t="n">
+      <c r="Y15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Z15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="X15" s="7" t="n">
+      <c r="AA15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Y15" s="7" t="n">
+      <c r="AB15" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="Z15" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AC15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="AD15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AE15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AH15" s="7" t="n">
         <v>0</v>
       </c>
@@ -46926,11 +46883,11 @@
         <v>0</v>
       </c>
       <c r="AL15" s="8" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM15" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 23; fotodetección previa: 61. Sensibilidad: todo estricto 81; todo +15 m 88.</t>
+          <t>Agentes: 24; fotodetección previa: 61. Sensibilidad: todo estricto 82; todo +15 m 89.</t>
         </is>
       </c>
     </row>
@@ -46944,10 +46901,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -46962,58 +46919,58 @@
         <v>0</v>
       </c>
       <c r="I16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="7" t="n">
+      <c r="M16" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="K16" s="7" t="n">
+      <c r="N16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="L16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="7" t="n">
+      <c r="O16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="O16" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="R16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="U16" s="7" t="n">
+      <c r="X16" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="V16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="7" t="n">
         <v>0</v>
@@ -47022,7 +46979,7 @@
         <v>0</v>
       </c>
       <c r="AC16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" s="7" t="n">
         <v>0</v>
@@ -47034,26 +46991,26 @@
         <v>0</v>
       </c>
       <c r="AG16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AI16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AL16" s="8" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="AM16" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 83; fotodetección previa: 0. Sensibilidad: todo estricto 82; todo +15 m 83.</t>
+          <t>Agentes: 92; fotodetección previa: 0. Sensibilidad: todo estricto 91; todo +15 m 92.</t>
         </is>
       </c>
     </row>
@@ -47064,7 +47021,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" s="7" t="n">
         <v>0</v>
@@ -47073,7 +47030,7 @@
         <v>0</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>0</v>
@@ -47088,31 +47045,31 @@
         <v>0</v>
       </c>
       <c r="J17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="K17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" s="7" t="n">
         <v>0</v>
@@ -47139,7 +47096,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
         <v>0</v>
@@ -47148,7 +47105,7 @@
         <v>0</v>
       </c>
       <c r="AD17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17" s="7" t="n">
         <v>0</v>
@@ -47160,7 +47117,7 @@
         <v>0</v>
       </c>
       <c r="AH17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="7" t="n">
         <v>0</v>
@@ -47169,14 +47126,14 @@
         <v>0</v>
       </c>
       <c r="AK17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL17" s="8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AM17" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 14; fotodetección previa: 0. Sensibilidad: todo estricto 14; todo +15 m 14.</t>
+          <t>Agentes: 17; fotodetección previa: 0. Sensibilidad: todo estricto 17; todo +15 m 17.</t>
         </is>
       </c>
     </row>
@@ -47256,7 +47213,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 27/08/2026    Código único: CU000000000912    Solicitud: SOL0000010882    Dirección ANSV: CARRERA 9 - CALLE 17 (SUR - NORTE)</t>
         </is>
       </c>
     </row>
@@ -47297,182 +47254,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Agosto 2023</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>Septiembre 2023</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2023</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2023</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2023</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Enero 2024</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2024</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2024</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Abril 2024</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2024</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Junio 2024</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Julio 2024</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2024</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2024</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2024</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2024</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2024</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Enero 2025</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2025</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2025</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Abril 2025</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2025</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Junio 2025</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Julio 2025</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2025</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2025</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2025</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2025</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2025</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>Enero 2026</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2026</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2026</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>Abril 2026</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>Junio 2026</t>
         </is>
       </c>
-      <c r="AJ7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Julio 2026</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -47694,10 +47651,10 @@
         <v>0</v>
       </c>
       <c r="AB9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="AC9" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AD9" s="7" t="n">
         <v>0</v>
@@ -47739,119 +47696,119 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="D10" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="H10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="I10" s="7" t="n">
         <v>27</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="J10" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>69</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>81</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="O10" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="P10" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="Q10" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>107</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="7" t="n">
         <v>85</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="T10" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>131</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>76</v>
       </c>
-      <c r="V10" s="7" t="n">
+      <c r="W10" s="7" t="n">
         <v>127</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="X10" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="Y10" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="AA10" s="7" t="n">
         <v>141</v>
       </c>
-      <c r="AA10" s="7" t="n">
+      <c r="AB10" s="7" t="n">
         <v>121</v>
       </c>
-      <c r="AB10" s="7" t="n">
+      <c r="AC10" s="7" t="n">
         <v>87</v>
       </c>
-      <c r="AC10" s="7" t="n">
+      <c r="AD10" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="AD10" s="7" t="n">
+      <c r="AE10" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="AE10" s="7" t="n">
+      <c r="AF10" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="AF10" s="7" t="n">
+      <c r="AG10" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="AG10" s="7" t="n">
+      <c r="AH10" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AI10" s="7" t="n">
         <v>47</v>
       </c>
-      <c r="AI10" s="7" t="n">
+      <c r="AJ10" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="AJ10" s="7" t="n">
+      <c r="AK10" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="AK10" s="7" t="n">
-        <v>28</v>
-      </c>
       <c r="AL10" s="8" t="n">
-        <v>2251</v>
+        <v>2233</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 256; fotodetección previa: 1995. Sensibilidad: todo estricto 2230; todo +15 m 2421.</t>
+          <t>Agentes: 260; fotodetección previa: 1973. Sensibilidad: todo estricto 2212; todo +15 m 2404.</t>
         </is>
       </c>
     </row>
@@ -47985,19 +47942,19 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -48006,26 +47963,26 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" s="7" t="n">
         <v>0</v>
       </c>
@@ -48072,10 +48029,10 @@
         <v>0</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="7" t="n">
         <v>0</v>
@@ -48108,10 +48065,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
@@ -48126,101 +48083,101 @@
         <v>0</v>
       </c>
       <c r="H13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="I13" s="7" t="n">
+      <c r="J13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="J13" s="7" t="n">
+      <c r="K13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="K13" s="7" t="n">
+      <c r="L13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="O13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="O13" s="7" t="n">
+      <c r="P13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="P13" s="7" t="n">
+      <c r="Q13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" s="7" t="n">
+      <c r="R13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="R13" s="7" t="n">
+      <c r="S13" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="S13" s="7" t="n">
+      <c r="T13" s="7" t="n">
         <v>10</v>
-      </c>
-      <c r="T13" s="7" t="n">
-        <v>8</v>
       </c>
       <c r="U13" s="7" t="n">
         <v>8</v>
       </c>
       <c r="V13" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="W13" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="W13" s="7" t="n">
+      <c r="X13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="Y13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Z13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="Z13" s="7" t="n">
+      <c r="AA13" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="AA13" s="7" t="n">
+      <c r="AB13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AB13" s="7" t="n">
+      <c r="AC13" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="AC13" s="7" t="n">
+      <c r="AD13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AD13" s="7" t="n">
+      <c r="AE13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AF13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AG13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AH13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AH13" s="7" t="n">
+      <c r="AI13" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="AI13" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="AJ13" s="7" t="n">
         <v>3</v>
       </c>
       <c r="AK13" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL13" s="8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AM13" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 5; fotodetección previa: 146. Sensibilidad: todo estricto 151; todo +15 m 168.</t>
+          <t>Agentes: 5; fotodetección previa: 145. Sensibilidad: todo estricto 150; todo +15 m 167.</t>
         </is>
       </c>
     </row>
@@ -48231,52 +48188,52 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="H14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="I14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="K14" s="7" t="n">
+      <c r="L14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="L14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="M14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="O14" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="O14" s="7" t="n">
+      <c r="P14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="Q14" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="Q14" s="7" t="n">
-        <v>4</v>
       </c>
       <c r="R14" s="7" t="n">
         <v>4</v>
@@ -48285,65 +48242,65 @@
         <v>4</v>
       </c>
       <c r="T14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="V14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="W14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="X14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="Y14" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Z14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="AA14" s="7" t="n">
         <v>13</v>
-      </c>
-      <c r="AA14" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="AB14" s="7" t="n">
         <v>6</v>
       </c>
       <c r="AC14" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AD14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AE14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AG14" s="7" t="n">
+      <c r="AH14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AH14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AI14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AJ14" s="7" t="n">
+      <c r="AK14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AK14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AL14" s="8" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AM14" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 12; fotodetección previa: 115. Sensibilidad: todo estricto 126; todo +15 m 140.</t>
+          <t>Agentes: 12; fotodetección previa: 114. Sensibilidad: todo estricto 125; todo +15 m 139.</t>
         </is>
       </c>
     </row>
@@ -48396,11 +48353,11 @@
         <v>0</v>
       </c>
       <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" s="7" t="n">
         <v>0</v>
       </c>
@@ -48441,10 +48398,10 @@
         <v>0</v>
       </c>
       <c r="AE15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="AF15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AG15" s="7" t="n">
         <v>0</v>
@@ -48480,16 +48437,16 @@
         <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="E16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>0</v>
@@ -48531,10 +48488,10 @@
         <v>0</v>
       </c>
       <c r="T16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16" s="7" t="n">
         <v>0</v>
@@ -48564,10 +48521,10 @@
         <v>0</v>
       </c>
       <c r="AE16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="7" t="n">
         <v>0</v>
@@ -48642,11 +48599,11 @@
         <v>0</v>
       </c>
       <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="7" t="n">
         <v>0</v>
       </c>
@@ -48663,10 +48620,10 @@
         <v>0</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="7" t="n">
         <v>0</v>
@@ -48675,10 +48632,10 @@
         <v>0</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="7" t="n">
         <v>0</v>
@@ -48687,11 +48644,11 @@
         <v>0</v>
       </c>
       <c r="AE17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AF17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" s="7" t="n">
         <v>0</v>
       </c>
@@ -48699,10 +48656,10 @@
         <v>0</v>
       </c>
       <c r="AI17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK17" s="7" t="n">
         <v>0</v>
@@ -48792,7 +48749,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Fecha inicio de operación: 02/09/2026 (POR CONFIRMAR: tomada del formulario ANSV de un equipo)    Id ANSV del equipo: pendiente</t>
+          <t>Fecha inicio de operación: 27/08/2026    Código único: CU000000000911    Solicitud: SOL0000010882    Dirección ANSV: CALLE 17 - CARRERA 8 (ESTE - OESTE)</t>
         </is>
       </c>
     </row>
@@ -48833,182 +48790,182 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
+          <t>Agosto 2023</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
           <t>Septiembre 2023</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2023</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2023</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2023</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>Enero 2024</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2024</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2024</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Abril 2024</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2024</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Junio 2024</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Julio 2024</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2024</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2024</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2024</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2024</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2024</t>
         </is>
       </c>
-      <c r="R7" s="5" t="inlineStr">
+      <c r="S7" s="5" t="inlineStr">
         <is>
           <t>Enero 2025</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2025</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2025</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>Abril 2025</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2025</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>Junio 2025</t>
         </is>
       </c>
-      <c r="X7" s="5" t="inlineStr">
+      <c r="Y7" s="5" t="inlineStr">
         <is>
           <t>Julio 2025</t>
         </is>
       </c>
-      <c r="Y7" s="5" t="inlineStr">
+      <c r="Z7" s="5" t="inlineStr">
         <is>
           <t>Agosto 2025</t>
         </is>
       </c>
-      <c r="Z7" s="5" t="inlineStr">
+      <c r="AA7" s="5" t="inlineStr">
         <is>
           <t>Septiembre 2025</t>
         </is>
       </c>
-      <c r="AA7" s="5" t="inlineStr">
+      <c r="AB7" s="5" t="inlineStr">
         <is>
           <t>Octubre 2025</t>
         </is>
       </c>
-      <c r="AB7" s="5" t="inlineStr">
+      <c r="AC7" s="5" t="inlineStr">
         <is>
           <t>Noviembre 2025</t>
         </is>
       </c>
-      <c r="AC7" s="5" t="inlineStr">
+      <c r="AD7" s="5" t="inlineStr">
         <is>
           <t>Diciembre 2025</t>
         </is>
       </c>
-      <c r="AD7" s="5" t="inlineStr">
+      <c r="AE7" s="5" t="inlineStr">
         <is>
           <t>Enero 2026</t>
         </is>
       </c>
-      <c r="AE7" s="5" t="inlineStr">
+      <c r="AF7" s="5" t="inlineStr">
         <is>
           <t>Febrero 2026</t>
         </is>
       </c>
-      <c r="AF7" s="5" t="inlineStr">
+      <c r="AG7" s="5" t="inlineStr">
         <is>
           <t>Marzo 2026</t>
         </is>
       </c>
-      <c r="AG7" s="5" t="inlineStr">
+      <c r="AH7" s="5" t="inlineStr">
         <is>
           <t>Abril 2026</t>
         </is>
       </c>
-      <c r="AH7" s="5" t="inlineStr">
+      <c r="AI7" s="5" t="inlineStr">
         <is>
           <t>Mayo 2026</t>
         </is>
       </c>
-      <c r="AI7" s="5" t="inlineStr">
+      <c r="AJ7" s="5" t="inlineStr">
         <is>
           <t>Junio 2026</t>
         </is>
       </c>
-      <c r="AJ7" s="5" t="inlineStr">
+      <c r="AK7" s="5" t="inlineStr">
         <is>
           <t>Julio 2026</t>
-        </is>
-      </c>
-      <c r="AK7" s="5" t="inlineStr">
-        <is>
-          <t>Agosto 2026</t>
         </is>
       </c>
       <c r="AL7" s="5" t="inlineStr">
@@ -49275,119 +49232,119 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C10" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="D10" s="7" t="n">
         <v>53</v>
       </c>
-      <c r="D10" s="7" t="n">
+      <c r="E10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="F10" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="G10" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>9</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>9</v>
       </c>
       <c r="I10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J10" s="7" t="n">
         <v>59</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="K10" s="7" t="n">
         <v>43</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="L10" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="L10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>9</v>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>23</v>
       </c>
       <c r="O10" s="7" t="n">
         <v>23</v>
       </c>
       <c r="P10" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="R10" s="7" t="n">
         <v>63</v>
       </c>
-      <c r="R10" s="7" t="n">
+      <c r="S10" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="S10" s="7" t="n">
+      <c r="T10" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="T10" s="7" t="n">
+      <c r="U10" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="U10" s="7" t="n">
+      <c r="V10" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="V10" s="7" t="n">
+      <c r="W10" s="7" t="n">
         <v>109</v>
       </c>
-      <c r="W10" s="7" t="n">
+      <c r="X10" s="7" t="n">
         <v>96</v>
       </c>
-      <c r="X10" s="7" t="n">
+      <c r="Y10" s="7" t="n">
         <v>104</v>
       </c>
-      <c r="Y10" s="7" t="n">
+      <c r="Z10" s="7" t="n">
         <v>102</v>
       </c>
-      <c r="Z10" s="7" t="n">
+      <c r="AA10" s="7" t="n">
         <v>105</v>
       </c>
-      <c r="AA10" s="7" t="n">
+      <c r="AB10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="AB10" s="7" t="n">
+      <c r="AC10" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="AC10" s="7" t="n">
+      <c r="AD10" s="7" t="n">
         <v>37</v>
       </c>
-      <c r="AD10" s="7" t="n">
+      <c r="AE10" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="AE10" s="7" t="n">
+      <c r="AF10" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="AF10" s="7" t="n">
+      <c r="AG10" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="AG10" s="7" t="n">
+      <c r="AH10" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="AH10" s="7" t="n">
+      <c r="AI10" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="AI10" s="7" t="n">
+      <c r="AJ10" s="7" t="n">
         <v>31</v>
       </c>
-      <c r="AJ10" s="7" t="n">
+      <c r="AK10" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="AK10" s="7" t="n">
-        <v>25</v>
-      </c>
       <c r="AL10" s="8" t="n">
-        <v>1640</v>
+        <v>1626</v>
       </c>
       <c r="AM10" s="9" t="inlineStr">
         <is>
-          <t>Agentes: 340; fotodetección previa: 1300. Sensibilidad: todo estricto 1603; todo +15 m 1780.</t>
+          <t>Agentes: 351; fotodetección previa: 1275. Sensibilidad: todo estricto 1589; todo +15 m 1766.</t>
         </is>
       </c>
     </row>
@@ -49422,10 +49379,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="7" t="n">
         <v>0</v>
@@ -49452,10 +49409,10 @@
         <v>0</v>
       </c>
       <c r="T11" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="7" t="n">
         <v>0</v>
@@ -49521,10 +49478,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
@@ -49542,10 +49499,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" s="7" t="n">
         <v>0</v>
@@ -49557,10 +49514,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="7" t="n">
         <v>0</v>
@@ -49608,10 +49565,10 @@
         <v>0</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="7" t="n">
         <v>0</v>
@@ -49644,11 +49601,11 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="D13" s="7" t="n">
         <v>0</v>
       </c>
@@ -49656,13 +49613,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>1</v>
@@ -49671,85 +49628,85 @@
         <v>1</v>
       </c>
       <c r="K13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L13" s="7" t="n">
+      <c r="M13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="M13" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="P13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="Q13" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="R13" s="7" t="n">
         <v>3</v>
       </c>
       <c r="S13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="T13" s="7" t="n">
+      <c r="U13" s="7" t="n">
         <v>9</v>
-      </c>
-      <c r="U13" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="V13" s="7" t="n">
         <v>6</v>
       </c>
       <c r="W13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X13" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="X13" s="7" t="n">
+      <c r="Y13" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="Y13" s="7" t="n">
+      <c r="Z13" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="Z13" s="7" t="n">
-        <v>3</v>
       </c>
       <c r="AA13" s="7" t="n">
         <v>3</v>
       </c>
       <c r="AB13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="AC13" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AD13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AE13" s="7" t="n">
+      <c r="AF13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" s="7" t="n">
+      <c r="AG13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AG13" s="7" t="n">
+      <c r="AH13" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="AH13" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AI13" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ13" s="7" t="n">
         <v>2</v>
       </c>
       <c r="AK13" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL13" s="8" t="n">
         <v>91</v>
@@ -49767,19 +49724,19 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0</v>
@@ -49791,77 +49748,77 @@
         <v>0</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="L14" s="7" t="n">
+      <c r="M14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="P14" s="7" t="n">
+      <c r="Q14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="R14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="S14" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="T14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="U14" s="7" t="n">
+      <c r="V14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="V14" s="7" t="n">
+      <c r="W14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="W14" s="7" t="n">
+      <c r="X14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="X14" s="7" t="n">
+      <c r="Y14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="Y14" s="7" t="n">
+      <c r="Z14" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="Z14" s="7" t="n">
+      <c r="AA14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AA14" s="7" t="n">
+      <c r="AB14" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="AB14" s="7" t="n">
+      <c r="AC14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="AC14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AD14" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14" s="7" t="n">
         <v>2</v>
       </c>
       <c r="AF14" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="AG14" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="AH14" s="7" t="n">
         <v>1</v>
       </c>
@@ -49872,7 +49829,7 @@
         <v>1</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL14" s="8" t="n">
         <v>80</v>
@@ -49899,10 +49856,10 @@
         <v>0</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>0</v>
@@ -49923,20 +49880,20 @@
         <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q15" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" s="7" t="n">
         <v>0</v>
       </c>
@@ -49977,10 +49934,10 @@
         <v>0</v>
       </c>
       <c r="AE15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="AF15" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AG15" s="7" t="n">
         <v>0</v>
@@ -50016,10 +49973,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -50100,10 +50057,10 @@
         <v>0</v>
       </c>
       <c r="AE16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="7" t="n">
         <v>0</v>
@@ -50172,17 +50129,17 @@
         <v>0</v>
       </c>
       <c r="N17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="O17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="P17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" s="7" t="n">
         <v>0</v>
       </c>
@@ -50199,10 +50156,10 @@
         <v>0</v>
       </c>
       <c r="W17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17" s="7" t="n">
         <v>0</v>
@@ -50211,10 +50168,10 @@
         <v>0</v>
       </c>
       <c r="AA17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" s="7" t="n">
         <v>0</v>
@@ -50223,10 +50180,10 @@
         <v>0</v>
       </c>
       <c r="AE17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="AF17" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="AG17" s="7" t="n">
         <v>0</v>
